--- a/artfynd/A 11575-2023 artfynd.xlsx
+++ b/artfynd/A 11575-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11575-2023 artfynd.xlsx
+++ b/artfynd/A 11575-2023 artfynd.xlsx
@@ -675,61 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82696257</v>
+        <v>96173152</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredebäckshult, Sm</t>
+          <t>Björkhaga, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507759.2641715485</v>
+        <v>507763</v>
       </c>
       <c r="R2" t="n">
-        <v>6275111.962600417</v>
+        <v>6275126</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,20 +769,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Birgitta Warodell</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Birgitta Warodell</t>
+          <t>Per Darell, Johan Blomby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -804,12 +797,7 @@
         <v>82696188</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507751.1908089232</v>
+        <v>507751</v>
       </c>
       <c r="R3" t="n">
-        <v>6275005.770520698</v>
+        <v>6275006</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +870,9 @@
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82696266</v>
+        <v>82696257</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -975,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507784.0045179616</v>
+        <v>507759</v>
       </c>
       <c r="R4" t="n">
-        <v>6275147.766829504</v>
+        <v>6275112</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,19 +981,9 @@
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82696317</v>
+        <v>82696266</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1046,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1101,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507822.1337591912</v>
+        <v>507784</v>
       </c>
       <c r="R5" t="n">
-        <v>6275097.775416357</v>
+        <v>6275148</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,19 +1092,9 @@
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,6 +1106,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1174,15 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82696392</v>
+        <v>82696317</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1157,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1222,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507883.7580764687</v>
+        <v>507822</v>
       </c>
       <c r="R6" t="n">
-        <v>6275160.055258419</v>
+        <v>6275098</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1255,19 +1203,9 @@
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-03-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,11 +1217,6 @@
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90920868</v>
+        <v>82696392</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,22 +1263,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredebäckshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507811.6843831282</v>
+        <v>507884</v>
       </c>
       <c r="R7" t="n">
-        <v>6275084.552733484</v>
+        <v>6275160</v>
       </c>
       <c r="S7" t="n">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1372,46 +1304,27 @@
           <t>Linneryd</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>G-Tin-0584</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Åtmionstone fem olika växtplatser</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
         <is>
           <t>Skogsmark</t>
         </is>
@@ -1419,7 +1332,7 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Birgitta Warodell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1427,72 +1340,56 @@
           <t>Birgitta Warodell</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96173152</v>
+        <v>90920868</v>
       </c>
       <c r="B8" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkhaga, Sm</t>
+          <t>Bredebäckshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507763.0975957767</v>
+        <v>507812</v>
       </c>
       <c r="R8" t="n">
-        <v>6275125.722996079</v>
+        <v>6275085</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1514,24 +1411,24 @@
           <t>Linneryd</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>G-Tin-0584</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-03-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Åtmionstone fem olika växtplatser</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,76 +1437,69 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Darell, Johan Blomby</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Birgitta Warodell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96228080</v>
+        <v>96173110</v>
       </c>
       <c r="B9" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1621,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507780.7112513072</v>
+        <v>507749</v>
       </c>
       <c r="R9" t="n">
-        <v>6275140.058923403</v>
+        <v>6275006</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1654,19 +1544,14 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>varav 3 blommande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1699,15 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96173250</v>
+        <v>96173182</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1734,7 +1614,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1751,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507887.624028158</v>
+        <v>507771</v>
       </c>
       <c r="R10" t="n">
-        <v>6275156.211601857</v>
+        <v>6275165</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1784,19 +1664,14 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>varav 8 blommande</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1829,15 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96232279</v>
+        <v>96173203</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1881,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507788.9830670864</v>
+        <v>507774</v>
       </c>
       <c r="R11" t="n">
-        <v>6275138.423825645</v>
+        <v>6275137</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1914,19 +1784,14 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>varav 4 blommande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1939,20 +1804,20 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Blomby</t>
+          <t>Per Darell</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Blomby, Per Darell</t>
+          <t>Per Darell, Johan Blomby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1962,12 +1827,7 @@
         <v>96173214</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2011,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507787.8866701775</v>
+        <v>507788</v>
       </c>
       <c r="R12" t="n">
-        <v>6275135.121012369</v>
+        <v>6275135</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2044,19 +1904,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2092,12 +1942,7 @@
         <v>96173236</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2141,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507813.7944695312</v>
+        <v>507814</v>
       </c>
       <c r="R13" t="n">
-        <v>6275135.719143046</v>
+        <v>6275135</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2174,19 +2019,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2224,15 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96173110</v>
+        <v>96173250</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2259,7 +2089,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2276,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507748.4344667824</v>
+        <v>507888</v>
       </c>
       <c r="R14" t="n">
-        <v>6275005.765447626</v>
+        <v>6275157</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2309,24 +2139,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>varav 3 blommande</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,15 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96173182</v>
+        <v>96232213</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2411,10 +2221,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507770.7430474143</v>
+        <v>507750</v>
       </c>
       <c r="R15" t="n">
-        <v>6275164.796311554</v>
+        <v>6275089</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2444,24 +2254,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>varav 8 blommande</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2474,35 +2269,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Darell</t>
+          <t>Johan Blomby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Darell, Johan Blomby</t>
+          <t>Johan Blomby, Per Darell</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96232213</v>
+        <v>96232279</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2529,7 +2319,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2546,10 +2336,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507750.4866301713</v>
+        <v>507789</v>
       </c>
       <c r="R16" t="n">
-        <v>6275088.840739859</v>
+        <v>6275138</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2579,19 +2369,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2624,47 +2404,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96173203</v>
+        <v>96228080</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2676,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507774.1023355199</v>
+        <v>507781</v>
       </c>
       <c r="R17" t="n">
-        <v>6275136.745931883</v>
+        <v>6275140</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2709,24 +2484,9 @@
           <t>2021-09-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-09-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>varav 4 blommande</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 11575-2023 artfynd.xlsx
+++ b/artfynd/A 11575-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696188</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696257</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696266</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696317</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1341,6 +1371,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82696392</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90920868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173110</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1701,6 +1746,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173182</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1821,6 +1871,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173203</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173214</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2056,6 +2116,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173236</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2171,6 +2236,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96173250</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2286,6 +2356,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96232213</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2401,6 +2476,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96232279</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,8 +2596,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96228080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>